--- a/scripts/family-data-template.xlsx
+++ b/scripts/family-data-template.xlsx
@@ -1195,16 +1195,16 @@
   <dimension ref="A1:J63"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.81640625" customWidth="1"/>
+    <col min="1" max="1" width="14.26953125" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="15.90625" customWidth="1"/>
-    <col min="4" max="4" width="3.36328125" customWidth="1"/>
-    <col min="5" max="5" width="10.6328125" style="12" customWidth="1"/>
+    <col min="4" max="4" width="5.453125" customWidth="1"/>
+    <col min="5" max="5" width="12.54296875" style="12" customWidth="1"/>
     <col min="6" max="6" width="11.6328125" style="12" customWidth="1"/>
     <col min="7" max="7" width="20.6328125" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="10" max="10" width="11.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
